--- a/Project_Members.xlsx
+++ b/Project_Members.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="23206"/>
+  <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="100" windowWidth="25000" windowHeight="13720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -52,17 +57,37 @@
   </si>
   <si>
     <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Xu Liyuan</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Tokyo Japan</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>JST(GMT +0900 hrs)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>liyuan9988@gmail.com</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Undergraduate Student</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -70,7 +95,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -101,8 +132,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -401,14 +432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="24.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="12" defaultColWidth="24.1640625" defaultRowHeight="17" x14ac:dyDescent="0"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,7 +459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -448,28 +479,64 @@
         <v>11</v>
       </c>
     </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="12" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0"/>
   <sheetData/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="12" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0"/>
   <sheetData/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>